--- a/public/templates/pelamar_template.xlsx
+++ b/public/templates/pelamar_template.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="81">
   <si>
     <t>nama</t>
   </si>
@@ -23,19 +23,28 @@
     <t>nik</t>
   </si>
   <si>
+    <t>tempat_lahir</t>
+  </si>
+  <si>
+    <t>tanggal_lahir</t>
+  </si>
+  <si>
     <t>no_telepon</t>
   </si>
   <si>
     <t>jenis_kelamin</t>
   </si>
   <si>
-    <t>tempat_lahir</t>
-  </si>
-  <si>
-    <t>tanggal_lahir</t>
-  </si>
-  <si>
-    <t>alamat</t>
+    <t>kewarganegaraan</t>
+  </si>
+  <si>
+    <t>status_pernikahan</t>
+  </si>
+  <si>
+    <t>alamat_domisili</t>
+  </si>
+  <si>
+    <t>alamat_ktp</t>
   </si>
   <si>
     <t>jenjang</t>
@@ -47,6 +56,12 @@
     <t>prodi_pendidikan</t>
   </si>
   <si>
+    <t>akreditas</t>
+  </si>
+  <si>
+    <t>no_ijazah</t>
+  </si>
+  <si>
     <t>ipk</t>
   </si>
   <si>
@@ -59,6 +74,12 @@
     <t>prodi_pendidikan_2</t>
   </si>
   <si>
+    <t>akreditas_2</t>
+  </si>
+  <si>
+    <t>no_ijazah_2</t>
+  </si>
+  <si>
     <t>ipk_2</t>
   </si>
   <si>
@@ -71,9 +92,27 @@
     <t>prodi_pendidikan_3</t>
   </si>
   <si>
+    <t>akreditas_3</t>
+  </si>
+  <si>
+    <t>no_ijazah_3</t>
+  </si>
+  <si>
     <t>ipk_3</t>
   </si>
   <si>
+    <t>jenis_tes_bahasa</t>
+  </si>
+  <si>
+    <t>skor_bahasa</t>
+  </si>
+  <si>
+    <t>tanggal_tes_bahasa</t>
+  </si>
+  <si>
+    <t>kategori_sertifikat</t>
+  </si>
+  <si>
     <t>nidn</t>
   </si>
   <si>
@@ -89,67 +128,136 @@
     <t>h_index</t>
   </si>
   <si>
-    <t>jenis_tes_bahasa</t>
-  </si>
-  <si>
-    <t>skor_bahasa</t>
-  </si>
-  <si>
-    <t>tanggal_tes_bahasa</t>
-  </si>
-  <si>
-    <t>kategori_sertifikat</t>
-  </si>
-  <si>
     <t>Budi Santoso</t>
   </si>
   <si>
+    <t>Jakarta</t>
+  </si>
+  <si>
+    <t>1990-01-15</t>
+  </si>
+  <si>
     <t>081234567890</t>
   </si>
   <si>
     <t>L</t>
   </si>
   <si>
-    <t>Jakarta</t>
-  </si>
-  <si>
-    <t>1990-01-15</t>
-  </si>
-  <si>
-    <t>Jl. Merdeka No. 123, Jakarta</t>
+    <t>WNI</t>
+  </si>
+  <si>
+    <t>Menikah</t>
+  </si>
+  <si>
+    <t>Jl. Merdeka No. 123, Jakarta Selatan</t>
+  </si>
+  <si>
+    <t>Jl. Pahlawan No. 5, Jakarta Pusat</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <t>Universitas Indonesia</t>
+  </si>
+  <si>
+    <t>Teknik Informatika</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>IJ-UI-2018-001</t>
   </si>
   <si>
     <t>S2</t>
   </si>
   <si>
-    <t>Universitas Indonesia</t>
-  </si>
-  <si>
-    <t>Teknik Informatika</t>
+    <t>Institut Teknologi Bandung</t>
+  </si>
+  <si>
+    <t>Teknik Komputer</t>
+  </si>
+  <si>
+    <t>IJ-ITB-2013-045</t>
+  </si>
+  <si>
+    <t>TOEFL_ITP</t>
+  </si>
+  <si>
+    <t>2023-06-15</t>
+  </si>
+  <si>
+    <t>kompetensi</t>
+  </si>
+  <si>
+    <t>0023015001</t>
+  </si>
+  <si>
+    <t>lektor</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Machine Learning</t>
+  </si>
+  <si>
+    <t>Siti Rahayu</t>
+  </si>
+  <si>
+    <t>Surabaya</t>
+  </si>
+  <si>
+    <t>1995-04-25</t>
+  </si>
+  <si>
+    <t>089876543210</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>Belum Menikah</t>
+  </si>
+  <si>
+    <t>Jl. Ahmad Yani No. 88, Surabaya</t>
+  </si>
+  <si>
+    <t>Institut Teknologi Sepuluh Nopember</t>
+  </si>
+  <si>
+    <t>Sistem Informasi</t>
+  </si>
+  <si>
+    <t>IJ-ITS-2020-099</t>
   </si>
   <si>
     <t>S1</t>
   </si>
   <si>
-    <t>ITB</t>
-  </si>
-  <si>
-    <t>Teknik Komputer</t>
-  </si>
-  <si>
-    <t>lektor</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence, Machine Learning</t>
-  </si>
-  <si>
-    <t>TOEFL_ITP</t>
-  </si>
-  <si>
-    <t>2023-06-15</t>
-  </si>
-  <si>
-    <t>kompetensi</t>
+    <t>IJ-ITS-2016-055</t>
+  </si>
+  <si>
+    <t>IELTS</t>
+  </si>
+  <si>
+    <t>2024-03-10</t>
+  </si>
+  <si>
+    <t>Data Science, Big Data Analytics</t>
+  </si>
+  <si>
+    <t>KETERANGAN WARNA:</t>
+  </si>
+  <si>
+    <t>Merah  = WAJIB diisi</t>
+  </si>
+  <si>
+    <t>Hijau  = OPSIONAL (boleh kosong)</t>
+  </si>
+  <si>
+    <t>Kuning = Keterangan kolom (baris 2)</t>
+  </si>
+  <si>
+    <t>File (foto, ijazah, dll) tidak diimpor lewat Excel.</t>
   </si>
 </sst>
 </file>
@@ -177,7 +285,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -187,6 +295,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF8b1515"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1a5e1a"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -203,9 +317,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
@@ -507,40 +624,49 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AM5"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="true" style="0"/>
-    <col min="2" max="2" width="18" customWidth="true" style="0"/>
-    <col min="3" max="3" width="18" customWidth="true" style="0"/>
-    <col min="4" max="4" width="18" customWidth="true" style="0"/>
-    <col min="5" max="5" width="18" customWidth="true" style="0"/>
-    <col min="6" max="6" width="18" customWidth="true" style="0"/>
-    <col min="7" max="7" width="18" customWidth="true" style="0"/>
-    <col min="8" max="8" width="18" customWidth="true" style="0"/>
-    <col min="9" max="9" width="18" customWidth="true" style="0"/>
-    <col min="10" max="10" width="18" customWidth="true" style="0"/>
-    <col min="11" max="11" width="18" customWidth="true" style="0"/>
-    <col min="12" max="12" width="18" customWidth="true" style="0"/>
-    <col min="13" max="13" width="18" customWidth="true" style="0"/>
-    <col min="14" max="14" width="18" customWidth="true" style="0"/>
-    <col min="15" max="15" width="18" customWidth="true" style="0"/>
-    <col min="16" max="16" width="18" customWidth="true" style="0"/>
-    <col min="17" max="17" width="18" customWidth="true" style="0"/>
-    <col min="18" max="18" width="18" customWidth="true" style="0"/>
-    <col min="19" max="19" width="18" customWidth="true" style="0"/>
-    <col min="20" max="20" width="18" customWidth="true" style="0"/>
-    <col min="21" max="21" width="18" customWidth="true" style="0"/>
-    <col min="22" max="22" width="18" customWidth="true" style="0"/>
-    <col min="23" max="23" width="18" customWidth="true" style="0"/>
-    <col min="24" max="24" width="18" customWidth="true" style="0"/>
-    <col min="25" max="25" width="18" customWidth="true" style="0"/>
-    <col min="26" max="26" width="18" customWidth="true" style="0"/>
-    <col min="27" max="27" width="18" customWidth="true" style="0"/>
-    <col min="28" max="28" width="18" customWidth="true" style="0"/>
+    <col min="1" max="1" width="22" customWidth="true" style="0"/>
+    <col min="2" max="2" width="22" customWidth="true" style="0"/>
+    <col min="3" max="3" width="22" customWidth="true" style="0"/>
+    <col min="4" max="4" width="22" customWidth="true" style="0"/>
+    <col min="5" max="5" width="22" customWidth="true" style="0"/>
+    <col min="6" max="6" width="22" customWidth="true" style="0"/>
+    <col min="7" max="7" width="22" customWidth="true" style="0"/>
+    <col min="8" max="8" width="22" customWidth="true" style="0"/>
+    <col min="9" max="9" width="22" customWidth="true" style="0"/>
+    <col min="10" max="10" width="22" customWidth="true" style="0"/>
+    <col min="11" max="11" width="22" customWidth="true" style="0"/>
+    <col min="12" max="12" width="22" customWidth="true" style="0"/>
+    <col min="13" max="13" width="22" customWidth="true" style="0"/>
+    <col min="14" max="14" width="22" customWidth="true" style="0"/>
+    <col min="15" max="15" width="22" customWidth="true" style="0"/>
+    <col min="16" max="16" width="22" customWidth="true" style="0"/>
+    <col min="17" max="17" width="22" customWidth="true" style="0"/>
+    <col min="18" max="18" width="22" customWidth="true" style="0"/>
+    <col min="19" max="19" width="22" customWidth="true" style="0"/>
+    <col min="20" max="20" width="22" customWidth="true" style="0"/>
+    <col min="21" max="21" width="22" customWidth="true" style="0"/>
+    <col min="22" max="22" width="22" customWidth="true" style="0"/>
+    <col min="23" max="23" width="22" customWidth="true" style="0"/>
+    <col min="24" max="24" width="22" customWidth="true" style="0"/>
+    <col min="25" max="25" width="22" customWidth="true" style="0"/>
+    <col min="26" max="26" width="22" customWidth="true" style="0"/>
+    <col min="27" max="27" width="22" customWidth="true" style="0"/>
+    <col min="28" max="28" width="22" customWidth="true" style="0"/>
+    <col min="29" max="29" width="22" customWidth="true" style="0"/>
+    <col min="30" max="30" width="22" customWidth="true" style="0"/>
+    <col min="31" max="31" width="22" customWidth="true" style="0"/>
+    <col min="32" max="32" width="22" customWidth="true" style="0"/>
+    <col min="33" max="33" width="22" customWidth="true" style="0"/>
+    <col min="34" max="34" width="22" customWidth="true" style="0"/>
+    <col min="35" max="35" width="22" customWidth="true" style="0"/>
+    <col min="36" max="36" width="22" customWidth="true" style="0"/>
+    <col min="37" max="37" width="22" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:39">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -559,149 +685,311 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="AC1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>76</v>
+      </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:39">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B2">
-        <v>1234567890123456</v>
+        <v>3201011501900001</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="J2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2">
-        <v>3.75</v>
+        <v>45</v>
+      </c>
+      <c r="K2" t="s">
+        <v>46</v>
       </c>
       <c r="L2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="M2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="N2" t="s">
-        <v>39</v>
-      </c>
-      <c r="O2">
-        <v>3.5</v>
-      </c>
-      <c r="P2"/>
-      <c r="Q2"/>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2">
-        <v>123456789</v>
+        <v>49</v>
+      </c>
+      <c r="O2" t="s">
+        <v>50</v>
+      </c>
+      <c r="P2">
+        <v>3.82</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>51</v>
+      </c>
+      <c r="R2" t="s">
+        <v>52</v>
+      </c>
+      <c r="S2" t="s">
+        <v>53</v>
+      </c>
+      <c r="T2" t="s">
+        <v>49</v>
       </c>
       <c r="U2" t="s">
-        <v>36</v>
-      </c>
-      <c r="V2" t="s">
-        <v>40</v>
-      </c>
-      <c r="W2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X2">
-        <v>15</v>
-      </c>
-      <c r="Y2" t="s">
+        <v>54</v>
+      </c>
+      <c r="V2">
+        <v>3.65</v>
+      </c>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD2">
+        <v>570</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AK2">
+        <v>12</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:39">
+      <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3">
+        <v>3578024504950002</v>
+      </c>
+      <c r="C3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" t="s">
         <v>42</v>
       </c>
-      <c r="Z2">
-        <v>550</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>44</v>
+      <c r="H3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3" t="s">
+        <v>68</v>
+      </c>
+      <c r="M3" t="s">
+        <v>69</v>
+      </c>
+      <c r="N3" t="s">
+        <v>49</v>
+      </c>
+      <c r="O3" t="s">
+        <v>70</v>
+      </c>
+      <c r="P3">
+        <v>3.91</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R3" t="s">
+        <v>68</v>
+      </c>
+      <c r="S3" t="s">
+        <v>69</v>
+      </c>
+      <c r="T3" t="s">
+        <v>49</v>
+      </c>
+      <c r="U3" t="s">
+        <v>72</v>
+      </c>
+      <c r="V3">
+        <v>3.78</v>
+      </c>
+      <c r="W3"/>
+      <c r="X3"/>
+      <c r="Y3"/>
+      <c r="Z3"/>
+      <c r="AA3"/>
+      <c r="AB3"/>
+      <c r="AC3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD3">
+        <v>6.5</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AF3"/>
+      <c r="AG3"/>
+      <c r="AH3"/>
+      <c r="AI3"/>
+      <c r="AJ3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK3">
+        <v>3</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:39">
+      <c r="AM4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39">
+      <c r="AM5" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
